--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -76,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +129,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFA0F2D7"/>
         <bgColor rgb="FFA0F2D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FEDC8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0F2D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -349,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -471,6 +481,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1018,12 +1030,20 @@
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="16" t="n"/>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>Xong 24/08/2026. Tài liệu triển khai API Gateway + kế hoạch này. 8 agent đã định danh trong dim_agent; ranh giới với dashboard hiện có đã chốt.</t>
+        </is>
+      </c>
       <c r="K4" s="17" t="n"/>
-      <c r="L4" s="17" t="n"/>
-      <c r="M4" s="17" t="n"/>
-      <c r="N4" s="17" t="n"/>
+      <c r="L4" s="53" t="n"/>
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
       <c r="O4" s="17" t="n"/>
       <c r="P4" s="17" t="n"/>
       <c r="Q4" s="17" t="n"/>
@@ -1042,9 +1062,9 @@
       <c r="AD4" s="17" t="n"/>
     </row>
     <row r="5" ht="73.5" customHeight="1" s="38">
-      <c r="A5" s="49" t="n"/>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
+      <c r="A5" s="47" t="n"/>
+      <c r="B5" s="47" t="n"/>
+      <c r="C5" s="47" t="n"/>
       <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Đo hiện trạng làm mốc so sánh sau khi có Gateway</t>
@@ -1066,11 +1086,19 @@
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="16" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>Xong 21/08/2026. Bộ số nền trước Gateway: 1.189 dòng · 867.657.110 token. Ba nguồn trên fact_usage_daily: billing 708.868.471 · monitoring 450.972.068 · app 110.640.605. Tỷ lệ quy được về người: 12,4%.</t>
+        </is>
+      </c>
       <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
+      <c r="L5" s="53" t="n"/>
+      <c r="M5" s="53" t="n"/>
       <c r="N5" s="17" t="n"/>
       <c r="O5" s="17" t="n"/>
       <c r="P5" s="17" t="n"/>
@@ -1116,12 +1144,20 @@
       <c r="F6" s="14" t="n"/>
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="16" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="16" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>Xong 24/08/2026. PostgreSQL 17 (token-ledger-postgres) là engine duy nhất — đường thoát SQLite đã gỡ. Schema do Alembic quản, chỉ tiến không lùi.</t>
+        </is>
+      </c>
       <c r="K6" s="17" t="n"/>
       <c r="L6" s="17" t="n"/>
-      <c r="M6" s="17" t="n"/>
-      <c r="N6" s="17" t="n"/>
+      <c r="M6" s="53" t="n"/>
+      <c r="N6" s="53" t="n"/>
       <c r="O6" s="17" t="n"/>
       <c r="P6" s="17" t="n"/>
       <c r="Q6" s="17" t="n"/>
@@ -1166,14 +1202,23 @@
         </is>
       </c>
       <c r="H7" s="16" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="16" t="n"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>14/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>Đang làm. Môi trường ĐO đã dựng được: LiteLLM 1.99.0 (fork litellm_rang_dong, commit f005afa146) trên Docker, 1 tuyến Google AI Studio, trả 200. Còn 7 tuyến còn lại và 3 môi trường.</t>
+        </is>
+      </c>
       <c r="K7" s="17" t="n"/>
       <c r="L7" s="17" t="n"/>
       <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="n"/>
-      <c r="O7" s="17" t="n"/>
-      <c r="P7" s="17" t="n"/>
+      <c r="N7" s="54" t="n"/>
+      <c r="O7" s="54" t="n"/>
+      <c r="P7" s="54" t="n"/>
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="17" t="n"/>
       <c r="S7" s="17" t="n"/>
@@ -1216,14 +1261,23 @@
         </is>
       </c>
       <c r="H8" s="16" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="16" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>14/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>Đang làm. 27/08 thêm vào docker-compose.yml (profile gateway): redis 7, 2 instance LiteLLM stateless, nginx làm load balancer, và database litellm riêng trên chính token-ledger-postgres. Chưa nghiệm thu bằng lượt chạy thật.</t>
+        </is>
+      </c>
       <c r="K8" s="17" t="n"/>
       <c r="L8" s="17" t="n"/>
       <c r="M8" s="17" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="17" t="n"/>
-      <c r="P8" s="17" t="n"/>
+      <c r="N8" s="54" t="n"/>
+      <c r="O8" s="54" t="n"/>
+      <c r="P8" s="54" t="n"/>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="17" t="n"/>
       <c r="S8" s="17" t="n"/>
@@ -1276,15 +1330,24 @@
         </is>
       </c>
       <c r="H9" s="16" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="16" t="n"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>21/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>Đang làm. Đã đo được JWT đăng nhập đi qua Gateway nguyên vẹn (260 ký tự, đủ claim). Chưa cấp Virtual Key cho agent nào.</t>
+        </is>
+      </c>
       <c r="K9" s="17" t="n"/>
       <c r="L9" s="17" t="n"/>
       <c r="M9" s="17" t="n"/>
       <c r="N9" s="17" t="n"/>
-      <c r="O9" s="17" t="n"/>
-      <c r="P9" s="17" t="n"/>
-      <c r="Q9" s="17" t="n"/>
+      <c r="O9" s="54" t="n"/>
+      <c r="P9" s="54" t="n"/>
+      <c r="Q9" s="54" t="n"/>
       <c r="R9" s="17" t="n"/>
       <c r="S9" s="17" t="n"/>
       <c r="T9" s="17" t="n"/>
@@ -1324,14 +1387,23 @@
         </is>
       </c>
       <c r="H10" s="16" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="16" t="n"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>14/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>Đo xong 26/08/2026: header khai ở user_header_name → cột end_user; toàn bộ header → proxy_server_request.metadata.headers (8/8 nguyên văn). Cần chốt: end_user giữ claim sub, không giữ cả chuỗi JWT — vì token đổi mỗi lần đăng nhập thì một người sẽ thành nhiều end_user.</t>
+        </is>
+      </c>
       <c r="K10" s="17" t="n"/>
       <c r="L10" s="17" t="n"/>
       <c r="M10" s="17" t="n"/>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="17" t="n"/>
-      <c r="P10" s="17" t="n"/>
+      <c r="N10" s="54" t="n"/>
+      <c r="O10" s="54" t="n"/>
+      <c r="P10" s="54" t="n"/>
       <c r="Q10" s="17" t="n"/>
       <c r="R10" s="17" t="n"/>
       <c r="S10" s="17" t="n"/>
@@ -1382,15 +1454,24 @@
         </is>
       </c>
       <c r="H11" s="16" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="16" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>21/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Đang làm. LiteLLM_SpendLogs có 34 cột, đã chép 4 dòng mẫu ra file. spend dựng lại được đến từng chữ số; Gateway ghi cả request THẤT BẠI nên fact_request bắt buộc có cột status. Còn đối chiếu 26 trường sheet Data Out.</t>
+        </is>
+      </c>
       <c r="K11" s="17" t="n"/>
       <c r="L11" s="17" t="n"/>
       <c r="M11" s="17" t="n"/>
-      <c r="N11" s="17" t="n"/>
-      <c r="O11" s="17" t="n"/>
-      <c r="P11" s="17" t="n"/>
-      <c r="Q11" s="17" t="n"/>
+      <c r="N11" s="54" t="n"/>
+      <c r="O11" s="54" t="n"/>
+      <c r="P11" s="54" t="n"/>
+      <c r="Q11" s="54" t="n"/>
       <c r="R11" s="17" t="n"/>
       <c r="S11" s="17" t="n"/>
       <c r="T11" s="17" t="n"/>
@@ -1431,16 +1512,21 @@
         </is>
       </c>
       <c r="H12" s="16" t="n"/>
-      <c r="I12" s="13" t="n"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>30/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J12" s="16" t="n"/>
       <c r="K12" s="17" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="17" t="n"/>
       <c r="N12" s="17" t="n"/>
       <c r="O12" s="17" t="n"/>
-      <c r="P12" s="17" t="n"/>
-      <c r="Q12" s="17" t="n"/>
-      <c r="R12" s="17" t="n"/>
+      <c r="P12" s="54" t="n"/>
+      <c r="Q12" s="54" t="n"/>
+      <c r="R12" s="54" t="n"/>
       <c r="S12" s="17" t="n"/>
       <c r="T12" s="17" t="n"/>
       <c r="U12" s="17" t="n"/>
@@ -1493,16 +1579,25 @@
         </is>
       </c>
       <c r="H13" s="16" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="16" t="n"/>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>30/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Khung 2 instance LiteLLM + load balancer đã có trong docker-compose.yml từ 27/08. Chưa có máy server thứ hai.</t>
+        </is>
+      </c>
       <c r="K13" s="17" t="n"/>
       <c r="L13" s="17" t="n"/>
       <c r="M13" s="17" t="n"/>
       <c r="N13" s="17" t="n"/>
-      <c r="O13" s="17" t="n"/>
-      <c r="P13" s="17" t="n"/>
-      <c r="Q13" s="17" t="n"/>
-      <c r="R13" s="17" t="n"/>
+      <c r="O13" s="54" t="n"/>
+      <c r="P13" s="54" t="n"/>
+      <c r="Q13" s="54" t="n"/>
+      <c r="R13" s="54" t="n"/>
       <c r="S13" s="17" t="n"/>
       <c r="T13" s="17" t="n"/>
       <c r="U13" s="17" t="n"/>
@@ -1543,7 +1638,12 @@
         </is>
       </c>
       <c r="H14" s="16" t="n"/>
-      <c r="I14" s="13" t="n"/>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>07/10/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J14" s="16" t="n"/>
       <c r="K14" s="17" t="n"/>
       <c r="L14" s="17" t="n"/>
@@ -1551,9 +1651,9 @@
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="17" t="n"/>
-      <c r="R14" s="17" t="n"/>
-      <c r="S14" s="17" t="n"/>
+      <c r="Q14" s="54" t="n"/>
+      <c r="R14" s="54" t="n"/>
+      <c r="S14" s="54" t="n"/>
       <c r="T14" s="17" t="n"/>
       <c r="U14" s="17" t="n"/>
       <c r="V14" s="17" t="n"/>
@@ -1593,7 +1693,12 @@
         </is>
       </c>
       <c r="H15" s="16" t="n"/>
-      <c r="I15" s="13" t="n"/>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>14/10/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J15" s="16" t="n"/>
       <c r="K15" s="17" t="n"/>
       <c r="L15" s="17" t="n"/>
@@ -1602,9 +1707,9 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="17" t="n"/>
-      <c r="R15" s="17" t="n"/>
-      <c r="S15" s="17" t="n"/>
-      <c r="T15" s="17" t="n"/>
+      <c r="R15" s="54" t="n"/>
+      <c r="S15" s="54" t="n"/>
+      <c r="T15" s="54" t="n"/>
       <c r="U15" s="17" t="n"/>
       <c r="V15" s="17" t="n"/>
       <c r="W15" s="17" t="n"/>
@@ -1652,16 +1757,25 @@
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="16" t="n"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>30/09/2026
+(dự kiến)</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>Chuẩn bị xong 24/08/2026: 10 chỗ đầu đọc đã hết lọc cứng source='app', hệ thống đón được nguồn thứ tư mà không phải sửa một câu SQL nào. Còn chuyển schema sang v2 (40/45 việc, đang chờ một người khác soát độc lập trước khi chạy).</t>
+        </is>
+      </c>
       <c r="K16" s="17" t="n"/>
       <c r="L16" s="17" t="n"/>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="17" t="n"/>
-      <c r="P16" s="17" t="n"/>
-      <c r="Q16" s="17" t="n"/>
-      <c r="R16" s="17" t="n"/>
+      <c r="M16" s="53" t="n"/>
+      <c r="N16" s="53" t="n"/>
+      <c r="O16" s="54" t="n"/>
+      <c r="P16" s="54" t="n"/>
+      <c r="Q16" s="54" t="n"/>
+      <c r="R16" s="54" t="n"/>
       <c r="S16" s="17" t="n"/>
       <c r="T16" s="17" t="n"/>
       <c r="U16" s="17" t="n"/>
@@ -1701,7 +1815,12 @@
         </is>
       </c>
       <c r="H17" s="16" t="n"/>
-      <c r="I17" s="13" t="n"/>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>07/10/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J17" s="16" t="n"/>
       <c r="K17" s="17" t="n"/>
       <c r="L17" s="17" t="n"/>
@@ -1709,9 +1828,9 @@
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="17" t="n"/>
       <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="17" t="n"/>
-      <c r="R17" s="17" t="n"/>
-      <c r="S17" s="17" t="n"/>
+      <c r="Q17" s="54" t="n"/>
+      <c r="R17" s="54" t="n"/>
+      <c r="S17" s="54" t="n"/>
       <c r="T17" s="17" t="n"/>
       <c r="U17" s="17" t="n"/>
       <c r="V17" s="17" t="n"/>
@@ -1749,7 +1868,12 @@
         </is>
       </c>
       <c r="H18" s="16" t="n"/>
-      <c r="I18" s="13" t="n"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>21/10/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J18" s="16" t="n"/>
       <c r="K18" s="17" t="n"/>
       <c r="L18" s="17" t="n"/>
@@ -1758,10 +1882,10 @@
       <c r="O18" s="17" t="n"/>
       <c r="P18" s="17" t="n"/>
       <c r="Q18" s="17" t="n"/>
-      <c r="R18" s="17" t="n"/>
-      <c r="S18" s="17" t="n"/>
-      <c r="T18" s="17" t="n"/>
-      <c r="U18" s="17" t="n"/>
+      <c r="R18" s="54" t="n"/>
+      <c r="S18" s="54" t="n"/>
+      <c r="T18" s="54" t="n"/>
+      <c r="U18" s="54" t="n"/>
       <c r="V18" s="17" t="n"/>
       <c r="W18" s="17" t="n"/>
       <c r="X18" s="17" t="n"/>
@@ -1809,7 +1933,12 @@
         </is>
       </c>
       <c r="H19" s="16" t="n"/>
-      <c r="I19" s="13" t="n"/>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>14/11/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J19" s="16" t="n"/>
       <c r="K19" s="17" t="n"/>
       <c r="L19" s="17" t="n"/>
@@ -1821,10 +1950,10 @@
       <c r="R19" s="17" t="n"/>
       <c r="S19" s="17" t="n"/>
       <c r="T19" s="17" t="n"/>
-      <c r="U19" s="17" t="n"/>
-      <c r="V19" s="17" t="n"/>
-      <c r="W19" s="17" t="n"/>
-      <c r="X19" s="17" t="n"/>
+      <c r="U19" s="54" t="n"/>
+      <c r="V19" s="54" t="n"/>
+      <c r="W19" s="54" t="n"/>
+      <c r="X19" s="54" t="n"/>
       <c r="Y19" s="17" t="n"/>
       <c r="Z19" s="17" t="n"/>
       <c r="AA19" s="17" t="n"/>
@@ -1858,7 +1987,12 @@
         </is>
       </c>
       <c r="H20" s="16" t="n"/>
-      <c r="I20" s="13" t="n"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>14/10/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J20" s="16" t="n"/>
       <c r="K20" s="17" t="n"/>
       <c r="L20" s="17" t="n"/>
@@ -1867,9 +2001,9 @@
       <c r="O20" s="17" t="n"/>
       <c r="P20" s="17" t="n"/>
       <c r="Q20" s="17" t="n"/>
-      <c r="R20" s="17" t="n"/>
-      <c r="S20" s="17" t="n"/>
-      <c r="T20" s="17" t="n"/>
+      <c r="R20" s="54" t="n"/>
+      <c r="S20" s="54" t="n"/>
+      <c r="T20" s="54" t="n"/>
       <c r="U20" s="17" t="n"/>
       <c r="V20" s="17" t="n"/>
       <c r="W20" s="17" t="n"/>
@@ -1907,7 +2041,12 @@
         </is>
       </c>
       <c r="H21" s="16" t="n"/>
-      <c r="I21" s="13" t="n"/>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>14/11/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J21" s="16" t="n"/>
       <c r="K21" s="17" t="n"/>
       <c r="L21" s="17" t="n"/>
@@ -1920,9 +2059,9 @@
       <c r="S21" s="17" t="n"/>
       <c r="T21" s="17" t="n"/>
       <c r="U21" s="17" t="n"/>
-      <c r="V21" s="17" t="n"/>
-      <c r="W21" s="17" t="n"/>
-      <c r="X21" s="17" t="n"/>
+      <c r="V21" s="54" t="n"/>
+      <c r="W21" s="54" t="n"/>
+      <c r="X21" s="54" t="n"/>
       <c r="Y21" s="17" t="n"/>
       <c r="Z21" s="17" t="n"/>
       <c r="AA21" s="17" t="n"/>
@@ -1966,7 +2105,12 @@
         </is>
       </c>
       <c r="H22" s="16" t="n"/>
-      <c r="I22" s="13" t="n"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>21/12/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="17" t="n"/>
       <c r="L22" s="17" t="n"/>
@@ -1982,14 +2126,14 @@
       <c r="V22" s="17" t="n"/>
       <c r="W22" s="17" t="n"/>
       <c r="X22" s="17" t="n"/>
-      <c r="Y22" s="17" t="n"/>
-      <c r="Z22" s="17" t="n"/>
-      <c r="AA22" s="17" t="n"/>
-      <c r="AB22" s="17" t="n"/>
-      <c r="AC22" s="17" t="n"/>
+      <c r="Y22" s="54" t="n"/>
+      <c r="Z22" s="54" t="n"/>
+      <c r="AA22" s="54" t="n"/>
+      <c r="AB22" s="54" t="n"/>
+      <c r="AC22" s="54" t="n"/>
       <c r="AD22" s="17" t="n"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1" s="38">
+    <row r="23" s="38">
       <c r="A23" s="47" t="n"/>
       <c r="B23" s="47" t="n"/>
       <c r="C23" s="47" t="n"/>
@@ -2016,7 +2160,12 @@
         </is>
       </c>
       <c r="H23" s="16" t="n"/>
-      <c r="I23" s="13" t="n"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>31/12/2026
+(dự kiến)</t>
+        </is>
+      </c>
       <c r="J23" s="16" t="n"/>
       <c r="K23" s="17" t="n"/>
       <c r="L23" s="17" t="n"/>
@@ -2036,8 +2185,8 @@
       <c r="Z23" s="17" t="n"/>
       <c r="AA23" s="17" t="n"/>
       <c r="AB23" s="17" t="n"/>
-      <c r="AC23" s="17" t="n"/>
-      <c r="AD23" s="17" t="n"/>
+      <c r="AC23" s="54" t="n"/>
+      <c r="AD23" s="54" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="38"/>
     <row r="25" ht="15.75" customHeight="1" s="38">
@@ -3038,9 +3187,10 @@
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="C4:C5"/>
+    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="B11:B12"/>
     <mergeCell ref="O2:R2"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B11:B12"/>
     <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="F2:F3"/>
@@ -3060,9 +3210,8 @@
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B6:B8"/>
-    <mergeCell ref="I2:I3"/>
     <mergeCell ref="S2:V2"/>
-    <mergeCell ref="W2:Z2"/>
+    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="J2:J3"/>
     <mergeCell ref="B4:B5"/>
@@ -3074,7 +3223,7 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="I2:I3"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -3713,7 +3862,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Dẫn xuất từ Gateway</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -3721,7 +3870,11 @@
           <t>Cột think trên dashboard</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>KHÔNG có cột riêng trong LiteLLM_SpendLogs. Quy tắc dẫn xuất, đo có đối chứng 26/08/2026: metadata.usage_object.completion_tokens_details.reasoning_tokens CÓ khoá ⇒ true; khoá VẮNG MẶT HOÀN TOÀN ⇒ false. Vắng mặt, không phải = 0 — đọc nhầm chỗ này thì mọi request đều thành 'có suy luận'.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="38">
       <c r="A17" s="3" t="n">
@@ -3750,7 +3903,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Gateway</t>
+          <t>Dẫn xuất từ Gateway</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -3760,7 +3913,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>text / image / audio</t>
+          <t>text / image / audio. KHÔNG có cột riêng. Dẫn xuất từ metadata.usage_object.completion_tokens_details.{text,audio,image}_tokens — khoá nào có giá trị thì đó là dạng đầu ra. Đo 26/08/2026: text_tokens = 22.</t>
         </is>
       </c>
     </row>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -75,8 +75,12 @@
       <color rgb="FF5A4FCF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="13"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -139,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA0F2D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -359,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -483,6 +492,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -761,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8.7109375" customWidth="1" style="38" min="1" max="1"/>
@@ -1041,9 +1054,9 @@
         </is>
       </c>
       <c r="K4" s="17" t="n"/>
-      <c r="L4" s="53" t="n"/>
-      <c r="M4" s="53" t="n"/>
-      <c r="N4" s="53" t="n"/>
+      <c r="L4" s="19" t="n"/>
+      <c r="M4" s="19" t="n"/>
+      <c r="N4" s="19" t="n"/>
       <c r="O4" s="17" t="n"/>
       <c r="P4" s="17" t="n"/>
       <c r="Q4" s="17" t="n"/>
@@ -1097,8 +1110,8 @@
         </is>
       </c>
       <c r="K5" s="17" t="n"/>
-      <c r="L5" s="53" t="n"/>
-      <c r="M5" s="53" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="n"/>
       <c r="N5" s="17" t="n"/>
       <c r="O5" s="17" t="n"/>
       <c r="P5" s="17" t="n"/>
@@ -1156,8 +1169,8 @@
       </c>
       <c r="K6" s="17" t="n"/>
       <c r="L6" s="17" t="n"/>
-      <c r="M6" s="53" t="n"/>
-      <c r="N6" s="53" t="n"/>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="n"/>
       <c r="O6" s="17" t="n"/>
       <c r="P6" s="17" t="n"/>
       <c r="Q6" s="17" t="n"/>
@@ -1208,17 +1221,17 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>Đang làm. Môi trường ĐO đã dựng được: LiteLLM 1.99.0 (fork litellm_rang_dong, commit f005afa146) trên Docker, 1 tuyến Google AI Studio, trả 200. Còn 7 tuyến còn lại và 3 môi trường.</t>
+      <c r="J7" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. Môi trường ĐO đã dựng: LiteLLM 1.99.0 (fork litellm_rang_dong, commit f005afa146) trên Docker, 1 tuyến Google AI Studio. 31/08/2026 agent đầu tiên (DMS) đã chạy THẬT qua tuyến này: 45 lượt vào LiteLLM_SpendLogs (40 thành công / 5 hỏng). Còn 7 tuyến và 3 môi trường dev / staging / production.</t>
         </is>
       </c>
       <c r="K7" s="17" t="n"/>
       <c r="L7" s="17" t="n"/>
       <c r="M7" s="17" t="n"/>
-      <c r="N7" s="54" t="n"/>
-      <c r="O7" s="54" t="n"/>
-      <c r="P7" s="54" t="n"/>
+      <c r="N7" s="56" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
       <c r="Q7" s="17" t="n"/>
       <c r="R7" s="17" t="n"/>
       <c r="S7" s="17" t="n"/>
@@ -1267,17 +1280,17 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>Đang làm. 27/08 thêm vào docker-compose.yml (profile gateway): redis 7, 2 instance LiteLLM stateless, nginx làm load balancer, và database litellm riêng trên chính token-ledger-postgres. Chưa nghiệm thu bằng lượt chạy thật.</t>
+      <c r="J8" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. 27/08 thêm vào docker-compose.yml (profile gateway): Redis 7 (1 primary + 1 replica) giữ trạng thái dùng chung, 2 instance LiteLLM stateless, nginx làm load balancer, và database litellm riêng trên chính token-ledger-postgres. 31/08 ĐÃ NGHIỆM THU bằng lượt chạy thật: request của DMS đi qua nginx → 2 instance → Redis dùng chung, ghi đủ 34 cột. Còn: chưa diễn tập tắt bớt instance, chưa đo bộ đếm hạn mức rpm/tpm.</t>
         </is>
       </c>
       <c r="K8" s="17" t="n"/>
       <c r="L8" s="17" t="n"/>
       <c r="M8" s="17" t="n"/>
-      <c r="N8" s="54" t="n"/>
-      <c r="O8" s="54" t="n"/>
-      <c r="P8" s="54" t="n"/>
+      <c r="N8" s="56" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="17" t="n"/>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="17" t="n"/>
       <c r="S8" s="17" t="n"/>
@@ -1336,18 +1349,18 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>Đang làm. Đã đo được JWT đăng nhập đi qua Gateway nguyên vẹn (260 ký tự, đủ claim). Chưa cấp Virtual Key cho agent nào.</t>
+      <c r="J9" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. JWT đăng nhập đi qua Gateway nguyên vẹn (260 ký tự, đủ claim). 31/08 đã cấp Virtual Key ĐẦU TIÊN — cho DMS: 35/45 lượt mang khoá này. Đo được 9/45 lượt vẫn đi bằng master key (phép kiểm nội bộ) — loại này chỉ quy được về agent nhờ tag chứ không nhờ khoá, nên cần trường virtual_key_id để tách ra. Còn 7 khoá cho 7 agent và cơ chế thu hồi.</t>
         </is>
       </c>
       <c r="K9" s="17" t="n"/>
       <c r="L9" s="17" t="n"/>
       <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="54" t="n"/>
-      <c r="P9" s="54" t="n"/>
-      <c r="Q9" s="54" t="n"/>
+      <c r="N9" s="56" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="17" t="n"/>
       <c r="R9" s="17" t="n"/>
       <c r="S9" s="17" t="n"/>
       <c r="T9" s="17" t="n"/>
@@ -1393,17 +1406,17 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>Đo xong 26/08/2026: header khai ở user_header_name → cột end_user; toàn bộ header → proxy_server_request.metadata.headers (8/8 nguyên văn). Cần chốt: end_user giữ claim sub, không giữ cả chuỗi JWT — vì token đổi mỗi lần đăng nhập thì một người sẽ thành nhiều end_user.</t>
+      <c r="J10" s="55" t="inlineStr">
+        <is>
+          <t>Đo xong 26/08/2026: header khai ở user_header_name → cột end_user; toàn bộ header → proxy_server_request.metadata.headers (8/8 nguyên văn). Hiện trạng 01/09 trên 45 lượt: end_user mang 19 'svc.dms-feedback', 15 'tuan.tran' (phép thử đã rút lại), 11 rỗng — NHƯNG cả 41 dòng nạp được đều quy về đúng MỘT tài khoản 949 svc.dms-feedback, đúng quy ước 'agent một-người-dùng' chốt 20/08. CẦN CHỐT: quy ước định danh áp cho cả 8 agent hay chỉ cho 2 agent nhiều người dùng (TLA Hợp Đồng, Ralli).</t>
         </is>
       </c>
       <c r="K10" s="17" t="n"/>
       <c r="L10" s="17" t="n"/>
       <c r="M10" s="17" t="n"/>
-      <c r="N10" s="54" t="n"/>
-      <c r="O10" s="54" t="n"/>
-      <c r="P10" s="54" t="n"/>
+      <c r="N10" s="56" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="17" t="n"/>
       <c r="Q10" s="17" t="n"/>
       <c r="R10" s="17" t="n"/>
       <c r="S10" s="17" t="n"/>
@@ -1460,18 +1473,18 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>Đang làm. LiteLLM_SpendLogs có 34 cột, đã chép 4 dòng mẫu ra file. spend dựng lại được đến từng chữ số; Gateway ghi cả request THẤT BẠI nên fact_request bắt buộc có cột status. Còn đối chiếu 26 trường sheet Data Out.</t>
+      <c r="J11" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. 31/08 fact_call ghi đủ 12 trường mục này yêu cầu: migration 006 thêm duration_ms, outcome, error_code. Độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google và bị từ chối — 0 là sự vắng mặt của phép đo, không phải một phép đo. Đối chiếu 26 trường sheet Data Out xong 01/09: CÓ 19/26 (kể cả trường tra qua dim_agent / dim_model / dim_unit), THIẾU 7 — trong đó 2 trường BẮT BUỘC là raw_model và virtual_key_id; cả hai đã có sẵn trong sổ Gateway (cột model và api_key), chỉ thiếu đường nạp.</t>
         </is>
       </c>
       <c r="K11" s="17" t="n"/>
       <c r="L11" s="17" t="n"/>
       <c r="M11" s="17" t="n"/>
-      <c r="N11" s="54" t="n"/>
-      <c r="O11" s="54" t="n"/>
-      <c r="P11" s="54" t="n"/>
-      <c r="Q11" s="54" t="n"/>
+      <c r="N11" s="56" t="n"/>
+      <c r="O11" s="56" t="n"/>
+      <c r="P11" s="17" t="n"/>
+      <c r="Q11" s="17" t="n"/>
       <c r="R11" s="17" t="n"/>
       <c r="S11" s="17" t="n"/>
       <c r="T11" s="17" t="n"/>
@@ -1518,15 +1531,19 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="n"/>
+      <c r="J12" s="55" t="inlineStr">
+        <is>
+          <t>Chưa làm. Nhưng số thô đã sẵn sàng từ 31/08: fact_call.duration_ms giữ độ trễ TỪNG LƯỢT, nên p50/p95/p99 theo ngày tính lại được chính xác thay vì nội suy từ histogram gộp — thùng histogram của nguồn monitoring rộng 33,6 giây, mọi phân vị rút từ nó mang sai số hàng chục giây. Quy ước dữ liệu (ngày theo giờ VN, trường không đo được ghi NULL) đã áp dụng ở migration 006.</t>
+        </is>
+      </c>
       <c r="K12" s="17" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="17" t="n"/>
       <c r="N12" s="17" t="n"/>
       <c r="O12" s="17" t="n"/>
-      <c r="P12" s="54" t="n"/>
-      <c r="Q12" s="54" t="n"/>
-      <c r="R12" s="54" t="n"/>
+      <c r="P12" s="17" t="n"/>
+      <c r="Q12" s="17" t="n"/>
+      <c r="R12" s="17" t="n"/>
       <c r="S12" s="17" t="n"/>
       <c r="T12" s="17" t="n"/>
       <c r="U12" s="17" t="n"/>
@@ -1585,19 +1602,19 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Khung 2 instance LiteLLM + load balancer đã có trong docker-compose.yml từ 27/08. Chưa có máy server thứ hai.</t>
+      <c r="J13" s="55" t="inlineStr">
+        <is>
+          <t>Khung 2 instance LiteLLM + nginx load balancer đã có trong docker-compose.yml từ 27/08, và 31/08 đã chạy lưu lượng THẬT qua khung này. Chưa có máy server thứ hai: cả 2 instance đang trên cùng một máy, nên chưa chứng minh được gì về chịu tải nhiều máy, cũng chưa thử thêm/bớt instance khi hệ thống đang chạy.</t>
         </is>
       </c>
       <c r="K13" s="17" t="n"/>
       <c r="L13" s="17" t="n"/>
       <c r="M13" s="17" t="n"/>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="54" t="n"/>
-      <c r="P13" s="54" t="n"/>
-      <c r="Q13" s="54" t="n"/>
-      <c r="R13" s="54" t="n"/>
+      <c r="N13" s="56" t="n"/>
+      <c r="O13" s="17" t="n"/>
+      <c r="P13" s="17" t="n"/>
+      <c r="Q13" s="17" t="n"/>
+      <c r="R13" s="17" t="n"/>
       <c r="S13" s="17" t="n"/>
       <c r="T13" s="17" t="n"/>
       <c r="U13" s="17" t="n"/>
@@ -1651,9 +1668,9 @@
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n"/>
       <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="54" t="n"/>
-      <c r="R14" s="54" t="n"/>
-      <c r="S14" s="54" t="n"/>
+      <c r="Q14" s="17" t="n"/>
+      <c r="R14" s="17" t="n"/>
+      <c r="S14" s="17" t="n"/>
       <c r="T14" s="17" t="n"/>
       <c r="U14" s="17" t="n"/>
       <c r="V14" s="17" t="n"/>
@@ -1707,9 +1724,9 @@
       <c r="O15" s="17" t="n"/>
       <c r="P15" s="17" t="n"/>
       <c r="Q15" s="17" t="n"/>
-      <c r="R15" s="54" t="n"/>
-      <c r="S15" s="54" t="n"/>
-      <c r="T15" s="54" t="n"/>
+      <c r="R15" s="17" t="n"/>
+      <c r="S15" s="17" t="n"/>
+      <c r="T15" s="17" t="n"/>
       <c r="U15" s="17" t="n"/>
       <c r="V15" s="17" t="n"/>
       <c r="W15" s="17" t="n"/>
@@ -1763,19 +1780,19 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Chuẩn bị xong 24/08/2026: 10 chỗ đầu đọc đã hết lọc cứng source='app', hệ thống đón được nguồn thứ tư mà không phải sửa một câu SQL nào. Còn chuyển schema sang v2 (40/45 việc, đang chờ một người khác soát độc lập trước khi chạy).</t>
+      <c r="J16" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. 24/08 gỡ hết lọc cứng source='app' ở 10 chỗ đầu đọc. Chuyển schema sang v2 ĐÃ XONG (45/45 việc). 31/08 nguồn thứ tư vào database thật: fact_usage_daily có đủ 4 nguồn, gateway 1 ngày / 45.187 token; ba bộ số cũ KHÔNG đổi một token nào (đối soát 24 khoá mốc). Còn: báo cáo đối chiếu chênh lệch giữa bốn nguồn.</t>
         </is>
       </c>
       <c r="K16" s="17" t="n"/>
       <c r="L16" s="17" t="n"/>
-      <c r="M16" s="53" t="n"/>
-      <c r="N16" s="53" t="n"/>
-      <c r="O16" s="54" t="n"/>
-      <c r="P16" s="54" t="n"/>
-      <c r="Q16" s="54" t="n"/>
-      <c r="R16" s="54" t="n"/>
+      <c r="M16" s="56" t="n"/>
+      <c r="N16" s="56" t="n"/>
+      <c r="O16" s="17" t="n"/>
+      <c r="P16" s="17" t="n"/>
+      <c r="Q16" s="17" t="n"/>
+      <c r="R16" s="17" t="n"/>
       <c r="S16" s="17" t="n"/>
       <c r="T16" s="17" t="n"/>
       <c r="U16" s="17" t="n"/>
@@ -1828,9 +1845,9 @@
       <c r="N17" s="17" t="n"/>
       <c r="O17" s="17" t="n"/>
       <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="54" t="n"/>
-      <c r="R17" s="54" t="n"/>
-      <c r="S17" s="54" t="n"/>
+      <c r="Q17" s="17" t="n"/>
+      <c r="R17" s="17" t="n"/>
+      <c r="S17" s="17" t="n"/>
       <c r="T17" s="17" t="n"/>
       <c r="U17" s="17" t="n"/>
       <c r="V17" s="17" t="n"/>
@@ -1874,18 +1891,22 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>Đang làm. 30/08/2026 commit 2f5b34d nối lại phần hiển thị user / phòng ban với database (+357 dòng web/js/app.js, +84 dòng web/js/api.js, thêm bộ kiểm filter-select-refresh). Dữ liệu nền đã đủ: cả 8/8 agent đều có số trong fact_usage_daily. Còn: ba biểu đồ tỷ lệ áp dụng theo phòng ban, người dùng hoạt động theo ngày, chi phí theo phòng ban.</t>
+        </is>
+      </c>
       <c r="K18" s="17" t="n"/>
       <c r="L18" s="17" t="n"/>
       <c r="M18" s="17" t="n"/>
-      <c r="N18" s="17" t="n"/>
+      <c r="N18" s="56" t="n"/>
       <c r="O18" s="17" t="n"/>
       <c r="P18" s="17" t="n"/>
       <c r="Q18" s="17" t="n"/>
-      <c r="R18" s="54" t="n"/>
-      <c r="S18" s="54" t="n"/>
-      <c r="T18" s="54" t="n"/>
-      <c r="U18" s="54" t="n"/>
+      <c r="R18" s="17" t="n"/>
+      <c r="S18" s="17" t="n"/>
+      <c r="T18" s="17" t="n"/>
+      <c r="U18" s="17" t="n"/>
       <c r="V18" s="17" t="n"/>
       <c r="W18" s="17" t="n"/>
       <c r="X18" s="17" t="n"/>
@@ -1950,10 +1971,10 @@
       <c r="R19" s="17" t="n"/>
       <c r="S19" s="17" t="n"/>
       <c r="T19" s="17" t="n"/>
-      <c r="U19" s="54" t="n"/>
-      <c r="V19" s="54" t="n"/>
-      <c r="W19" s="54" t="n"/>
-      <c r="X19" s="54" t="n"/>
+      <c r="U19" s="17" t="n"/>
+      <c r="V19" s="17" t="n"/>
+      <c r="W19" s="17" t="n"/>
+      <c r="X19" s="17" t="n"/>
       <c r="Y19" s="17" t="n"/>
       <c r="Z19" s="17" t="n"/>
       <c r="AA19" s="17" t="n"/>
@@ -1993,17 +2014,21 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="n"/>
+      <c r="J20" s="55" t="inlineStr">
+        <is>
+          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. Còn: backend/check_api.py, và phép kiểm đối chiếu token cache của Gateway với SKU cache trên hoá đơn Google.</t>
+        </is>
+      </c>
       <c r="K20" s="17" t="n"/>
       <c r="L20" s="17" t="n"/>
       <c r="M20" s="17" t="n"/>
-      <c r="N20" s="17" t="n"/>
-      <c r="O20" s="17" t="n"/>
+      <c r="N20" s="56" t="n"/>
+      <c r="O20" s="56" t="n"/>
       <c r="P20" s="17" t="n"/>
       <c r="Q20" s="17" t="n"/>
-      <c r="R20" s="54" t="n"/>
-      <c r="S20" s="54" t="n"/>
-      <c r="T20" s="54" t="n"/>
+      <c r="R20" s="17" t="n"/>
+      <c r="S20" s="17" t="n"/>
+      <c r="T20" s="17" t="n"/>
       <c r="U20" s="17" t="n"/>
       <c r="V20" s="17" t="n"/>
       <c r="W20" s="17" t="n"/>
@@ -2059,9 +2084,9 @@
       <c r="S21" s="17" t="n"/>
       <c r="T21" s="17" t="n"/>
       <c r="U21" s="17" t="n"/>
-      <c r="V21" s="54" t="n"/>
-      <c r="W21" s="54" t="n"/>
-      <c r="X21" s="54" t="n"/>
+      <c r="V21" s="17" t="n"/>
+      <c r="W21" s="17" t="n"/>
+      <c r="X21" s="17" t="n"/>
       <c r="Y21" s="17" t="n"/>
       <c r="Z21" s="17" t="n"/>
       <c r="AA21" s="17" t="n"/>
@@ -2126,11 +2151,11 @@
       <c r="V22" s="17" t="n"/>
       <c r="W22" s="17" t="n"/>
       <c r="X22" s="17" t="n"/>
-      <c r="Y22" s="54" t="n"/>
-      <c r="Z22" s="54" t="n"/>
-      <c r="AA22" s="54" t="n"/>
-      <c r="AB22" s="54" t="n"/>
-      <c r="AC22" s="54" t="n"/>
+      <c r="Y22" s="17" t="n"/>
+      <c r="Z22" s="17" t="n"/>
+      <c r="AA22" s="17" t="n"/>
+      <c r="AB22" s="17" t="n"/>
+      <c r="AC22" s="17" t="n"/>
       <c r="AD22" s="17" t="n"/>
     </row>
     <row r="23" s="38">
@@ -2185,8 +2210,8 @@
       <c r="Z23" s="17" t="n"/>
       <c r="AA23" s="17" t="n"/>
       <c r="AB23" s="17" t="n"/>
-      <c r="AC23" s="54" t="n"/>
-      <c r="AD23" s="54" t="n"/>
+      <c r="AC23" s="17" t="n"/>
+      <c r="AD23" s="17" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="38"/>
     <row r="25" ht="15.75" customHeight="1" s="38">
@@ -2198,19 +2223,25 @@
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Đã hoàn thành</t>
+          <t>Thực hiện xong</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" s="38">
-      <c r="C26" s="21" t="n"/>
+      <c r="C26" s="56" t="n"/>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Theo kế hoạch / đang làm</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="14.25" customHeight="1" s="38"/>
+          <t>Đang thực hiện</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1" s="38">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ô trống: chưa bắt đầu</t>
+        </is>
+      </c>
+    </row>
     <row r="28" ht="14.25" customHeight="1" s="38"/>
     <row r="29" ht="14.25" customHeight="1" s="38"/>
     <row r="30" ht="14.25" customHeight="1" s="38"/>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -1282,14 +1282,14 @@
       </c>
       <c r="J8" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 27/08 thêm vào docker-compose.yml (profile gateway): Redis 7 (1 primary + 1 replica) giữ trạng thái dùng chung, 2 instance LiteLLM stateless, nginx làm load balancer, và database litellm riêng trên chính token-ledger-postgres. 31/08 ĐÃ NGHIỆM THU bằng lượt chạy thật: request của DMS đi qua nginx → 2 instance → Redis dùng chung, ghi đủ 34 cột. Còn: chưa diễn tập tắt bớt instance, chưa đo bộ đếm hạn mức rpm/tpm.</t>
+          <t>Xong 01/09/2026. 27/08 thêm vào docker-compose.yml (profile gateway): Redis 7 (1 primary + 1 replica), 2 instance LiteLLM stateless, nginx làm load balancer, database litellm riêng trên token-ledger-postgres. 31/08 nghiệm thu load balancer bằng lưu lượng thật của DMS. 01/09 nghiệm thu CACHE DÙNG CHUNG bằng một agent: hai request giống hệt nhau qua load balancer rơi vào HAI instance khác nhau, lượt hai trúng cache trên instance chưa từng ghi cache — 4.222 ms xuống 261 ms, cùng một id phản hồi, Redis giữ 13 khoá. Chứng minh trạng thái nằm ở Redis chứ không phải bộ nhớ từng tiến trình. Cache sau đó TẮT LẠI có chủ ý: đo được lượt trúng cache ghi spend = 0 nhưng VẪN ghi đủ 352 token, nên bật thật sẽ làm token qua Gateway phồng so với token Google tính tiền. Bật lại sau khi xong báo cáo đối chiếu bốn nguồn.</t>
         </is>
       </c>
       <c r="K8" s="17" t="n"/>
       <c r="L8" s="17" t="n"/>
       <c r="M8" s="17" t="n"/>
-      <c r="N8" s="56" t="n"/>
-      <c r="O8" s="17" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
       <c r="P8" s="17" t="n"/>
       <c r="Q8" s="17" t="n"/>
       <c r="R8" s="17" t="n"/>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="J11" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 fact_call ghi đủ 12 trường mục này yêu cầu: migration 006 thêm duration_ms, outcome, error_code. Độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google và bị từ chối — 0 là sự vắng mặt của phép đo, không phải một phép đo. Đối chiếu 26 trường sheet Data Out xong 01/09: CÓ 19/26 (kể cả trường tra qua dim_agent / dim_model / dim_unit), THIẾU 7 — trong đó 2 trường BẮT BUỘC là raw_model và virtual_key_id; cả hai đã có sẵn trong sổ Gateway (cột model và api_key), chỉ thiếu đường nạp.</t>
+          <t>Đang làm. 31/08 migration 006 thêm duration_ms, outcome, error_code — độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google. 01/09 migration 007 thêm nốt raw_model, virtual_key_id và cache_hit. ĐỐI CHIẾU 26 TRƯỜNG SHEET DATA OUT: 19/26 → 21/26, và 0 TRƯỜNG BẮT BUỘC CÒN THIẾU. Cả 12 trường mà mục này liệt kê đều đã có. 5 trường còn thiếu đều không bắt buộc (thinking_enabled, output_modality, cost_is_estimated, retry_count, fallback_used). Đo được khi nạp: 7/41 lượt (17,1%) đi bằng khoá quản trị chung chứ không phải khoá agent — trước khi có virtual_key_id thì không tách ra được. Nghiệm thu: 24/24 khoá mốc khớp, audit 42 phép kiểm / 38 đạt / 4 lưu ý / 0 hỏng.</t>
         </is>
       </c>
       <c r="K11" s="17" t="n"/>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="J11" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 migration 006 thêm duration_ms, outcome, error_code — độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google. 01/09 migration 007 thêm nốt raw_model, virtual_key_id và cache_hit. ĐỐI CHIẾU 26 TRƯỜNG SHEET DATA OUT: 19/26 → 21/26, và 0 TRƯỜNG BẮT BUỘC CÒN THIẾU. Cả 12 trường mà mục này liệt kê đều đã có. 5 trường còn thiếu đều không bắt buộc (thinking_enabled, output_modality, cost_is_estimated, retry_count, fallback_used). Đo được khi nạp: 7/41 lượt (17,1%) đi bằng khoá quản trị chung chứ không phải khoá agent — trước khi có virtual_key_id thì không tách ra được. Nghiệm thu: 24/24 khoá mốc khớp, audit 42 phép kiểm / 38 đạt / 4 lưu ý / 0 hỏng.</t>
+          <t>Đang làm. 31/08 migration 006 thêm duration_ms, outcome, error_code — độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google. 01/09 migration 007 thêm nốt raw_model, virtual_key_id và cache_hit. ĐỐI CHIẾU 26 TRƯỜNG SHEET DATA OUT: 19/26 → 21/26, và 0 TRƯỜNG BẮT BUỘC CÒN THIẾU. Cả 12 trường mà mục này liệt kê đều đã có. 5 trường còn thiếu đều không bắt buộc (thinking_enabled, output_modality, cost_is_estimated, retry_count, fallback_used). Đo được khi nạp: 7/41 lượt (17,1%) đi bằng khoá quản trị chung chứ không phải khoá agent — trước khi có virtual_key_id thì không tách ra được. Nghiệm thu: 24/24 khoá mốc khớp, audit 42 phép kiểm / 38 đạt / 4 lưu ý / 0 hỏng. 03/09 migration 008 thêm output_modality và thinking_enabled — cả hai nằm CÙNG khối completion_tokens_details (bản đầu của đề xuất trỏ nhầm sang prompt_tokens_details; hai khối đều có text_tokens 42/42 nên đọc nhầm vẫn ra số, chỉ là số của chiều ngược lại). DATA OUT: 21/26 → 23/26 CÓ ĐƯỜNG NẠP — nhưng 2 trong 23 trường đó CHƯA CÓ SỐ, và cần đọc đúng như vậy: thinking_enabled 0/41 vì hai dòng duy nhất có reasoning_tokens (=342) không mang tag định danh agent nên bị loại ở khâu nạp (fact_call.agent_id là NOT NULL); cached_tokens 0/41, chưa kết luận được (đã loại trừ khả năng LiteLLM không ánh xạ; phép thử quyết định là hoá đơn ngày 31/08, chưa về). output_modality 38/41 — ba dòng rỗng là ba lượt hỏng, lượt hỏng không có phản hồi để dán nhãn. Bẫy đo được 03/09: DO UPDATE KHÔNG đủ khi thêm cột, phải chạy load_gateway.py --full, nếu không chỉ 6/41 dòng nhận cột mới. Nghiệm thu 03/09: 24/24 khoá mốc khớp, audit 54 phép kiểm / 50 đạt / 4 lưu ý / 0 hỏng.</t>
         </is>
       </c>
       <c r="K11" s="17" t="n"/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="J12" s="55" t="inlineStr">
         <is>
-          <t>Chưa làm. Nhưng số thô đã sẵn sàng từ 31/08: fact_call.duration_ms giữ độ trễ TỪNG LƯỢT, nên p50/p95/p99 theo ngày tính lại được chính xác thay vì nội suy từ histogram gộp — thùng histogram của nguồn monitoring rộng 33,6 giây, mọi phân vị rút từ nó mang sai số hàng chục giây. Quy ước dữ liệu (ngày theo giờ VN, trường không đo được ghi NULL) đã áp dụng ở migration 006.</t>
+          <t>Xong 03/09/2026, sớm 27 ngày so với mốc. Nhưng số thô đã sẵn sàng từ 31/08: fact_call.duration_ms giữ độ trễ TỪNG LƯỢT, nên p50/p95/p99 theo ngày tính lại được chính xác thay vì nội suy từ histogram gộp — thùng histogram của nguồn monitoring rộng 33,6 giây, mọi phân vị rút từ nó mang sai số hàng chục giây. Quy ước dữ liệu (ngày theo giờ VN, trường không đo được ghi NULL) đã áp dụng ở migration 006. Migration 008 dựng fact_usage_hourly — cùng năm chiều khoá như bảng ngày, chỉ đổi day thành hour: 3.327 dòng trên 1.751 giờ / 153 ngày (monitoring 2.624 · app 698 · gateway 5). KHÔNG có nguồn billing và đó là có chủ ý: hoá đơn Google chỉ tính theo NGÀY, chia đều cho 24 giờ sẽ cho ra một con số bịa — người đọc biết nguồn nào vắng bằng cách truy vấn cột source. Tổng theo giờ khớp tổng theo ngày cho TỪNG NGUỒN (bộ dựng tự dừng nếu lệch). Endpoint GET /api/usage-hourly, BẮT BUỘC có khoảng thời gian, khác 9 endpoint kia. Phân vị Gateway nay tính CHÍNH XÁC từ duration_ms thô: p95 ngày 31/08 = 1,822 s, khớp đúng con số change 006 tính tay; hai cột p95_bucket_* để NULL vì số thô không có sai số nội suy. Mỗi nguồn một dòng, không gộp trung bình. Chưa giải thích được: hai nguồn lệch 31,9 lần cho cùng agent 6 (thủ công p95 58,206 s vs gateway 1,822 s) và chưa ngày nào hai nguồn cùng có số để kiểm chứng lẫn nhau.</t>
         </is>
       </c>
       <c r="K12" s="17" t="n"/>
@@ -1760,7 +1760,7 @@
       <c r="E16" s="14" t="inlineStr">
         <is>
           <t>- Thêm nguồn dữ liệu Gateway vào trong danh sách các nguồn hiện có.
-- Kiểm tra và báo cáo đối chiếu chênh lệch giữa bốn nguồn.</t>
+- Phép kiểm đối chiếu nguồn, chạy trong quá trình phát triển để kiểm soát logic và thuật toán. KHÔNG phải báo cáo giao nộp.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="J16" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 24/08 gỡ hết lọc cứng source='app' ở 10 chỗ đầu đọc. Chuyển schema sang v2 ĐÃ XONG (45/45 việc). 31/08 nguồn thứ tư vào database thật: fact_usage_daily có đủ 4 nguồn, gateway 1 ngày / 45.187 token; ba bộ số cũ KHÔNG đổi một token nào (đối soát 24 khoá mốc). Còn: báo cáo đối chiếu chênh lệch giữa bốn nguồn.</t>
+          <t>Đang làm. 24/08 gỡ hết lọc cứng source='app' ở 10 chỗ đầu đọc. Chuyển schema sang v2 ĐÃ XONG (45/45 việc). 31/08 nguồn thứ tư vào database thật: fact_usage_daily có đủ 4 nguồn, gateway 1 ngày / 45.187 token; ba bộ số cũ KHÔNG đổi một token nào (đối soát 24 khoá mốc). 03/09 định nghĩa lại vế 2 cho đúng bản chất: đây là phép kiểm nội bộ, không phải báo cáo giao nộp. Đo: 0 ngày có đủ cả bốn nguồn — ngày duy nhất có Gateway (31/08) thì billing và monitoring đã dừng ở 29/08, app ở 30/08. Nên vế này KHÔNG chặn được bằng công sức. Ràng buộc "chạy song song tối thiểu 2 tuần trên agent production" GỠ KHỎI ĐƯỜNG GĂNG của STT 6 — nó vẫn là sản phẩm của STT 7 dòng 19, chỉ không còn chặn STT 6. Phép kiểm đối chiếu nay chạy được ngay: audit_db.py có 68 phép, trong đó nhóm F đối chiếu tổng theo giờ với tổng theo ngày CHO TỪNG NGUỒN, nhóm G đối chiếu chiều tài khoản với usage_resolved trên cả token lẫn calls, và ba phép chéo kiểm với /api/health qua một đường tính hoàn toàn khác.</t>
         </is>
       </c>
       <c r="K16" s="17" t="n"/>
@@ -1838,7 +1838,11 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>XONG 03/09/2026, sớm 34 ngày so với mốc. VẾ 1 — truy vấn và endpoint mới: GET /api/usage-hourly (bắt buộc có khoảng thời gian, khác 9 endpoint kia); /api/usage-by-account đọc view mới usage_by_account_resolved, phủ 8/8 agent thay vì 2/8 (1.453 dòng / 60 tài khoản); /api/performance đọc latency_resolved nên phân vị Gateway lên được dashboard — p95 ngày 31/08 = 1,822 s tính CHÍNH XÁC từ duration_ms thô thay vì nội suy trong ô histogram rộng trung bình 31,3 giây. VẾ 2 — kỷ luật chỉ-đọc: phát hiện và bịt một lỗ hổng chưa ai biết. rebuild_db.py bước 1 gọi DROP SCHEMA, xoá sạch GRANT của vai api_readonly, và CẢ HAI bộ kiểm đều báo lành trong lúc API mù — đo 02/09: container api chạy 38 phút trên database nó không đọc nổi. Nay rebuild_db.py có bước 10 kiểm quyền và DỪNG nếu thiếu; check_api.py hỏi MÁY CHỦ qua HTTP thay vì hỏi kết nối của chính nó. Tái tạo được lỗi: sau rebuild_db.py, api_readonly đọc 0/26 bảng+view, phép mới HỎNG còn phép cũ vẫn báo ĐẠT. Nghiệm thu: audit 68/64/4/0, check_api 27/27.</t>
+        </is>
+      </c>
       <c r="K17" s="17" t="n"/>
       <c r="L17" s="17" t="n"/>
       <c r="M17" s="17" t="n"/>
@@ -1871,7 +1875,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>- Ba biểu đồ có dữ liệu cho cả 8 agent: tỷ lệ áp dụng theo phòng ban, người dùng hoạt động theo ngày, chi phí theo phòng ban.</t>
+          <t>- Ba biểu đồ có dữ liệu cho cả 8 agent: tỷ lệ áp dụng theo agent, người dùng hoạt động theo ngày, chi phí theo phòng ban.</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -1893,7 +1897,7 @@
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>Đang làm. 30/08/2026 commit 2f5b34d nối lại phần hiển thị user / phòng ban với database (+357 dòng web/js/app.js, +84 dòng web/js/api.js, thêm bộ kiểm filter-select-refresh). Dữ liệu nền đã đủ: cả 8/8 agent đều có số trong fact_usage_daily. Còn: ba biểu đồ tỷ lệ áp dụng theo phòng ban, người dùng hoạt động theo ngày, chi phí theo phòng ban.</t>
+          <t>Đang làm. 30/08/2026 commit 2f5b34d nối lại phần hiển thị user / phòng ban với database (+357 dòng web/js/app.js, +84 dòng web/js/api.js, thêm bộ kiểm filter-select-refresh). Dữ liệu nền đã đủ: cả 8/8 agent đều có số trong fact_usage_daily. 03/09 — 2/3 biểu đồ XONG. View usage_by_account_resolved phủ 8/8 agent (1.453 dòng / 60 tài khoản / token 915.969.971 và calls 122.504, cả hai khớp usage_resolved). ① Tỷ lệ áp dụng: XONG, 8/8 agent — sáu agent dịch vụ mẫu số 1 là ĐÚNG theo quy ước account chốt 20/08; câu chữ "theo phòng ban" đã sửa thành "theo agent". ② Người dùng hoạt động theo ngày: XONG, từ 2/8 lên 8/8 agent — đường cong sẽ nhảy lên vì dữ liệu mới, không phải lỗi; đây là đếm TÀI KHOẢN chứ không phải người ngoài đời. ③ Chi phí theo phòng ban: CHƯA — donut vẫn khoá theo primaryUnit(), tức đơn vị GỐC của agent, nên 130 đơn vị chỉ ra 8 lát: sáu lát là tên agent đổi nhãn, hai lát là gốc cây (cả công ty). Không lát nào là một phòng ban. Tiền thì CÓ (từ /api/usage), cái sai là chiều phòng ban. Muốn đúng thì cần cost_usd xuống tới mức tài khoản, mà tiền chỉ tồn tại ở mức (ngày, agent, model) — chia đều cho các tài khoản là bịa. Việc này chưa nằm trong change nào.</t>
         </is>
       </c>
       <c r="K18" s="17" t="n"/>
@@ -2016,7 +2020,7 @@
       </c>
       <c r="J20" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. Còn: backend/check_api.py, và phép kiểm đối chiếu token cache của Gateway với SKU cache trên hoá đơn Google.</t>
+          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. 03/09: audit_db.py thêm nhóm F (12 phép) — tổng giờ khớp tổng ngày theo từng nguồn, không có billing trong bảng giờ, mọi giờ cắt đúng đầu giờ, phân vị số thô không mang ô histogram và ngược lại phân vị nội suy phải giữ ô. Chạy đầy đủ: 54 phép / 50 đạt / 4 lưu ý / 0 hỏng. backend/check_api.py XONG: thêm 6 phép cho endpoint theo giờ, chạy 25/25 đạt. Trong lúc làm, phát hiện check_api.py mang một phép kiểm LỖI THỜI từ 31/08 — nó so tiền API với riêng fact_billing_daily trong khi migration 005 đã cố ý đổ tiền Gateway vào usage_resolved ($307,360850 + $0,021305 = $307,382155), nên nó báo HỎNG cho một hệ thống đang đúng; đã sửa CÔNG THỨC theo đúng phép của audit_db.py, không nới ngưỡng. CÒN LẠI: phép kiểm đối chiếu token cache Gateway với SKU cache hoá đơn Google — CHƯA THỰC HIỆN ĐƯỢC, không phải vì thiếu công: vế Gateway luôn rỗng (cached_tokens 0/41) và hoá đơn dừng 29/08 trong khi lượt Gateway ở 31/08, hai nguồn chưa có ngày chung.</t>
         </is>
       </c>
       <c r="K20" s="17" t="n"/>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J20" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. 03/09: audit_db.py thêm nhóm F (12 phép) — tổng giờ khớp tổng ngày theo từng nguồn, không có billing trong bảng giờ, mọi giờ cắt đúng đầu giờ, phân vị số thô không mang ô histogram và ngược lại phân vị nội suy phải giữ ô. Chạy đầy đủ: 54 phép / 50 đạt / 4 lưu ý / 0 hỏng. backend/check_api.py XONG: thêm 6 phép cho endpoint theo giờ, chạy 25/25 đạt. Trong lúc làm, phát hiện check_api.py mang một phép kiểm LỖI THỜI từ 31/08 — nó so tiền API với riêng fact_billing_daily trong khi migration 005 đã cố ý đổ tiền Gateway vào usage_resolved ($307,360850 + $0,021305 = $307,382155), nên nó báo HỎNG cho một hệ thống đang đúng; đã sửa CÔNG THỨC theo đúng phép của audit_db.py, không nới ngưỡng. CÒN LẠI: phép kiểm đối chiếu token cache Gateway với SKU cache hoá đơn Google — CHƯA THỰC HIỆN ĐƯỢC, không phải vì thiếu công: vế Gateway luôn rỗng (cached_tokens 0/41) và hoá đơn dừng 29/08 trong khi lượt Gateway ở 31/08, hai nguồn chưa có ngày chung.</t>
+          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. 03/09: audit_db.py thêm nhóm F (12 phép) — tổng giờ khớp tổng ngày theo từng nguồn, không có billing trong bảng giờ, mọi giờ cắt đúng đầu giờ, phân vị số thô không mang ô histogram và ngược lại phân vị nội suy phải giữ ô. Chạy đầy đủ: 54 phép / 50 đạt / 4 lưu ý / 0 hỏng. backend/check_api.py XONG: thêm 6 phép cho endpoint theo giờ, chạy 25/25 đạt. Trong lúc làm, phát hiện check_api.py mang một phép kiểm LỖI THỜI từ 31/08 — nó so tiền API với riêng fact_billing_daily trong khi migration 005 đã cố ý đổ tiền Gateway vào usage_resolved ($307,360850 + $0,021305 = $307,382155), nên nó báo HỎNG cho một hệ thống đang đúng; đã sửa CÔNG THỨC theo đúng phép của audit_db.py, không nới ngưỡng. 03/09 chiều — XONG cả hai vế, nhưng vế 2 XONG theo nghĩa PHÉP KIỂM ĐÃ CÓ VÀ NÓ NÓI THẲNG LÀ CHƯA KIỂM ĐƯỢC, không phải theo nghĩa đã đối chiếu xong. VẾ 1 — bốn phép mà mục này liệt kê: KHOÁ NGOẠI nay đọc từ pg_constraint thay vì một danh sách gõ tay; đo được danh sách cũ đã trôi mất 13/36 quan hệ, trong đó 6 do chính migration 008 tạo ra sáng cùng ngày — nó tụt trong im lặng vì nhãn vẫn báo "Foreign keys (23 relations)" ĐẠT, mà 23 là số quan hệ ĐƯỢC KHAI chứ không phải số CÓ THẬT. Thêm mốc số lượng (&gt;= 36) để bắt chiều ngược lại: xoá một khoá ngoại thì danh sách tự sinh vẫn xanh. NGÀY TƯƠNG LAI bỏ ngưỡng ghim '2026-12-31' (sang 2027 mọi dòng thật đều bị coi là tương lai), thay bằng CURRENT_DATE + 1, và soi 5 bảng thay vì 1 — kể cả fact_call, nơi Gateway ghi từng lượt. TÀI KHOẢN LẠ và SỐ KHỚP HOÁ ĐƠN đã có từ 31/08, nay bổ sung mẫu số quan sát. VẾ 2 — phép kiểm đối chiếu token cache ĐÃ VIẾT XONG (nhóm H của audit_db.py), so theo ngày × agent trên đúng những ngày CẢ HAI nguồn cùng có, ngưỡng 1% chốt TRƯỚC kỳ đo theo đúng kỷ luật STT 7 dòng 19. Chạy hôm nay ra CHƯA KIỂM ĐƯỢC: gateway 31/08→31/08 (1 ngày), hoá đơn 05/01→29/08 (214 ngày), SỐ NGÀY GIAO NHAU = 0; và vế Gateway rỗng sạch (cached_tokens 0/41). ĐIỀU KIỆN ĐỂ NÓ CHẠY: một ngày mà Gateway và hoá đơn Google cùng có dữ liệu — hoá đơn về trễ ~1 ngày nên chỉ cần Gateway chạy thêm vài ngày liên tục là đủ. SỬA MỘT HÌNH DẠNG LỖI, không chỉ thêm phép kiểm: mọi phép kiểm theo nguồn nay khai CẢ MẪU SỐ. Trước đây "0 dòng xấu" trên 0 dòng gateway báo ĐẠT — nó không phân biệt "Gateway ghi đúng" với "Gateway không ghi gì cả", và đó đúng là hình dạng đã để API mù 38 phút ngày 02/09. Nghiệm thu bằng cách tái tạo trên một tập rỗng THẬT (fact_perf_daily không có dòng gateway nào), không dựng database giả. NGHIỆM THU: audit_db.py 72 phép / 65 đạt / 7 lưu ý / 0 hỏng (mốc 68/64/4/0 — lưu ý tăng 4→7 là ĐÚNG, ba cái mới đều là chỗ trước nay báo đạt mà chưa quan sát gì, và bốn lưu ý cũ giữ nguyên); check_api.py 31/31 (mốc 27/27); chạy hai lần liên tiếp số không đổi; usage_resolved khớp 4/4 khoá — change này không đụng một dòng dữ liệu nào.</t>
         </is>
       </c>
       <c r="K20" s="17" t="n"/>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -1475,7 +1475,7 @@
       </c>
       <c r="J11" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 migration 006 thêm duration_ms, outcome, error_code — độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google. 01/09 migration 007 thêm nốt raw_model, virtual_key_id và cache_hit. ĐỐI CHIẾU 26 TRƯỜNG SHEET DATA OUT: 19/26 → 21/26, và 0 TRƯỜNG BẮT BUỘC CÒN THIẾU. Cả 12 trường mà mục này liệt kê đều đã có. 5 trường còn thiếu đều không bắt buộc (thinking_enabled, output_modality, cost_is_estimated, retry_count, fallback_used). Đo được khi nạp: 7/41 lượt (17,1%) đi bằng khoá quản trị chung chứ không phải khoá agent — trước khi có virtual_key_id thì không tách ra được. Nghiệm thu: 24/24 khoá mốc khớp, audit 42 phép kiểm / 38 đạt / 4 lưu ý / 0 hỏng. 03/09 migration 008 thêm output_modality và thinking_enabled — cả hai nằm CÙNG khối completion_tokens_details (bản đầu của đề xuất trỏ nhầm sang prompt_tokens_details; hai khối đều có text_tokens 42/42 nên đọc nhầm vẫn ra số, chỉ là số của chiều ngược lại). DATA OUT: 21/26 → 23/26 CÓ ĐƯỜNG NẠP — nhưng 2 trong 23 trường đó CHƯA CÓ SỐ, và cần đọc đúng như vậy: thinking_enabled 0/41 vì hai dòng duy nhất có reasoning_tokens (=342) không mang tag định danh agent nên bị loại ở khâu nạp (fact_call.agent_id là NOT NULL); cached_tokens 0/41, chưa kết luận được (đã loại trừ khả năng LiteLLM không ánh xạ; phép thử quyết định là hoá đơn ngày 31/08, chưa về). output_modality 38/41 — ba dòng rỗng là ba lượt hỏng, lượt hỏng không có phản hồi để dán nhãn. Bẫy đo được 03/09: DO UPDATE KHÔNG đủ khi thêm cột, phải chạy load_gateway.py --full, nếu không chỉ 6/41 dòng nhận cột mới. Nghiệm thu 03/09: 24/24 khoá mốc khớp, audit 54 phép kiểm / 50 đạt / 4 lưu ý / 0 hỏng.</t>
+          <t>Đang làm. 31/08 migration 006 thêm duration_ms, outcome, error_code — độ trễ 609–3.136 ms trên 38/38 lượt thành công; lượt hỏng ghi NULL vì LiteLLM ghi 0 cho MỌI lượt hỏng, kể cả lượt đã gọi tới Google. 01/09 migration 007 thêm nốt raw_model, virtual_key_id và cache_hit. ĐỐI CHIẾU 26 TRƯỜNG SHEET DATA OUT: 19/26 → 21/26, và 0 TRƯỜNG BẮT BUỘC CÒN THIẾU. Cả 12 trường mà mục này liệt kê đều đã có. 5 trường còn thiếu đều không bắt buộc (thinking_enabled, output_modality, cost_is_estimated, retry_count, fallback_used). Đo được khi nạp: 7/41 lượt (17,1%) đi bằng khoá quản trị chung chứ không phải khoá agent — trước khi có virtual_key_id thì không tách ra được. Nghiệm thu: 24/24 khoá mốc khớp, audit 42 phép kiểm / 38 đạt / 4 lưu ý / 0 hỏng. 03/09 migration 008 thêm output_modality và thinking_enabled — cả hai nằm CÙNG khối completion_tokens_details (bản đầu của đề xuất trỏ nhầm sang prompt_tokens_details; hai khối đều có text_tokens 42/42 nên đọc nhầm vẫn ra số, chỉ là số của chiều ngược lại). DATA OUT: 21/26 → 23/26 CÓ ĐƯỜNG NẠP — nhưng 2 trong 23 trường đó CHƯA CÓ SỐ, và cần đọc đúng như vậy: thinking_enabled 0/41 vì hai dòng duy nhất có reasoning_tokens (=342) không mang tag định danh agent nên bị loại ở khâu nạp (fact_call.agent_id là NOT NULL); cached_tokens 0/41, chưa kết luận được (đã loại trừ khả năng LiteLLM không ánh xạ; phép thử quyết định là hoá đơn ngày 31/08, chưa về). output_modality 38/41 — ba dòng rỗng là ba lượt hỏng, lượt hỏng không có phản hồi để dán nhãn. Bẫy đo được 03/09: DO UPDATE KHÔNG đủ khi thêm cột, phải chạy load_gateway.py --full, nếu không chỉ 6/41 dòng nhận cột mới. Nghiệm thu 03/09: 24/24 khoá mốc khớp, audit 54 phép kiểm / 50 đạt / 4 lưu ý / 0 hỏng. 05/09 ĐÍNH CHÍNH MỘT CÂU Ở TRÊN: dòng này viết "cached_tokens 0/41, chưa kết luận được ... phép thử quyết định là hoá đơn ngày 31/08". PHÉP THỬ ĐÓ KHÔNG THẮNG ĐƯỢC. Khoá của Gateway là FREE TIER — bằng chứng nằm ngay trong tên phép đo Google trả về (quota/generate_content_free_tier_input_token_count/usage, limit_name ...-FreeTier) — nên lưu lượng này sẽ KHÔNG BAO GIỜ lên hoá đơn, chờ bao lâu cũng vậy. Đường đối chiếu bắt buộc đi qua Cloud Monitoring, không qua fact_billing_daily. 05/09 ĐO ĐƯỢC MỘT KHOẢN THIẾU MÀ BẢN GHI KHÔNG NÓI RA: 12 trường mục này liệt kê đều CÓ MẶT, nhưng GIÁ TRỊ của chúng ở lượt hỏng là ĐIỀU SỔ KHAI chứ không phải ĐIỀU ĐÃ TIÊU. Ngày 31/08 nhà cung cấp báo 41 request với response_code = 200 cho TẤT CẢ, không một lỗi nào, trong khi sổ LiteLLM ghi 5 lượt hỏng — hai lượt đã được phục vụ xong và đã tiêu token thật, sổ ghi cho chúng 0 token 0 ms. Chênh 6.334 token = 12,29% của riêng ngày đó. Tên gọi: failed_is_not_free. load_gateway.py nay in token của lượt hỏng KÈM chữ "điều sổ khai", và audit_db.py nhóm I đối chiếu với số của nhà cung cấp. KHOẢN NỢ CÒN LẠI: 6 dòng sổ nguồn (760 token) không vào được fact_call, trong đó có một lượt THÀNH CÔNG 25 token, vì không có tag khớp dim_agent.code mà fact_call.agent_id là NOT NULL. Đã bác bỏ hai nghi can cũ (mốc nước, ranh giới ngày) bằng --full: vẫn inserted 0. Sửa được nó cần một agent "không quy được" hoặc agent_id cho phép NULL — chưa làm.</t>
         </is>
       </c>
       <c r="K11" s="17" t="n"/>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="J16" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 24/08 gỡ hết lọc cứng source='app' ở 10 chỗ đầu đọc. Chuyển schema sang v2 ĐÃ XONG (45/45 việc). 31/08 nguồn thứ tư vào database thật: fact_usage_daily có đủ 4 nguồn, gateway 1 ngày / 45.187 token; ba bộ số cũ KHÔNG đổi một token nào (đối soát 24 khoá mốc). 03/09 định nghĩa lại vế 2 cho đúng bản chất: đây là phép kiểm nội bộ, không phải báo cáo giao nộp. Đo: 0 ngày có đủ cả bốn nguồn — ngày duy nhất có Gateway (31/08) thì billing và monitoring đã dừng ở 29/08, app ở 30/08. Nên vế này KHÔNG chặn được bằng công sức. Ràng buộc "chạy song song tối thiểu 2 tuần trên agent production" GỠ KHỎI ĐƯỜNG GĂNG của STT 6 — nó vẫn là sản phẩm của STT 7 dòng 19, chỉ không còn chặn STT 6. Phép kiểm đối chiếu nay chạy được ngay: audit_db.py có 68 phép, trong đó nhóm F đối chiếu tổng theo giờ với tổng theo ngày CHO TỪNG NGUỒN, nhóm G đối chiếu chiều tài khoản với usage_resolved trên cả token lẫn calls, và ba phép chéo kiểm với /api/health qua một đường tính hoàn toàn khác.</t>
+          <t>Đang làm. 24/08 gỡ hết lọc cứng source='app' ở 10 chỗ đầu đọc. Chuyển schema sang v2 ĐÃ XONG (45/45 việc). 31/08 nguồn thứ tư vào database thật: fact_usage_daily có đủ 4 nguồn, gateway 1 ngày / 45.187 token; ba bộ số cũ KHÔNG đổi một token nào (đối soát 24 khoá mốc). 03/09 định nghĩa lại vế 2 cho đúng bản chất: đây là phép kiểm nội bộ, không phải báo cáo giao nộp. Đo: 0 ngày có đủ cả bốn nguồn — ngày duy nhất có Gateway (31/08) thì billing và monitoring đã dừng ở 29/08, app ở 30/08. Nên vế này KHÔNG chặn được bằng công sức. Ràng buộc "chạy song song tối thiểu 2 tuần trên agent production" GỠ KHỎI ĐƯỜNG GĂNG của STT 6 — nó vẫn là sản phẩm của STT 7 dòng 19, chỉ không còn chặn STT 6. Phép kiểm đối chiếu nay chạy được ngay: audit_db.py có 68 phép, trong đó nhóm F đối chiếu tổng theo giờ với tổng theo ngày CHO TỪNG NGUỒN, nhóm G đối chiếu chiều tài khoản với usage_resolved trên cả token lẫn calls, và ba phép chéo kiểm với /api/health qua một đường tính hoàn toàn khác. 04/09 đóng nốt đường NẠP: refresh_gateway.py trước đây chỉ làm mới 2 bảng trong số 4 bảng mà Gateway chạm tới, nên phân vị và bảng theo giờ giữ số cũ trong im lặng sau mỗi lần nạp. Nay 4 bước, và bản tóm tắt in đủ 4 bảng thay vì 2 (commit 131d3b5).</t>
         </is>
       </c>
       <c r="K16" s="17" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="J20" s="55" t="inlineStr">
         <is>
-          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. 03/09: audit_db.py thêm nhóm F (12 phép) — tổng giờ khớp tổng ngày theo từng nguồn, không có billing trong bảng giờ, mọi giờ cắt đúng đầu giờ, phân vị số thô không mang ô histogram và ngược lại phân vị nội suy phải giữ ô. Chạy đầy đủ: 54 phép / 50 đạt / 4 lưu ý / 0 hỏng. backend/check_api.py XONG: thêm 6 phép cho endpoint theo giờ, chạy 25/25 đạt. Trong lúc làm, phát hiện check_api.py mang một phép kiểm LỖI THỜI từ 31/08 — nó so tiền API với riêng fact_billing_daily trong khi migration 005 đã cố ý đổ tiền Gateway vào usage_resolved ($307,360850 + $0,021305 = $307,382155), nên nó báo HỎNG cho một hệ thống đang đúng; đã sửa CÔNG THỨC theo đúng phép của audit_db.py, không nới ngưỡng. 03/09 chiều — XONG cả hai vế, nhưng vế 2 XONG theo nghĩa PHÉP KIỂM ĐÃ CÓ VÀ NÓ NÓI THẲNG LÀ CHƯA KIỂM ĐƯỢC, không phải theo nghĩa đã đối chiếu xong. VẾ 1 — bốn phép mà mục này liệt kê: KHOÁ NGOẠI nay đọc từ pg_constraint thay vì một danh sách gõ tay; đo được danh sách cũ đã trôi mất 13/36 quan hệ, trong đó 6 do chính migration 008 tạo ra sáng cùng ngày — nó tụt trong im lặng vì nhãn vẫn báo "Foreign keys (23 relations)" ĐẠT, mà 23 là số quan hệ ĐƯỢC KHAI chứ không phải số CÓ THẬT. Thêm mốc số lượng (&gt;= 36) để bắt chiều ngược lại: xoá một khoá ngoại thì danh sách tự sinh vẫn xanh. NGÀY TƯƠNG LAI bỏ ngưỡng ghim '2026-12-31' (sang 2027 mọi dòng thật đều bị coi là tương lai), thay bằng CURRENT_DATE + 1, và soi 5 bảng thay vì 1 — kể cả fact_call, nơi Gateway ghi từng lượt. TÀI KHOẢN LẠ và SỐ KHỚP HOÁ ĐƠN đã có từ 31/08, nay bổ sung mẫu số quan sát. VẾ 2 — phép kiểm đối chiếu token cache ĐÃ VIẾT XONG (nhóm H của audit_db.py), so theo ngày × agent trên đúng những ngày CẢ HAI nguồn cùng có, ngưỡng 1% chốt TRƯỚC kỳ đo theo đúng kỷ luật STT 7 dòng 19. Chạy hôm nay ra CHƯA KIỂM ĐƯỢC: gateway 31/08→31/08 (1 ngày), hoá đơn 05/01→29/08 (214 ngày), SỐ NGÀY GIAO NHAU = 0; và vế Gateway rỗng sạch (cached_tokens 0/41). ĐIỀU KIỆN ĐỂ NÓ CHẠY: một ngày mà Gateway và hoá đơn Google cùng có dữ liệu — hoá đơn về trễ ~1 ngày nên chỉ cần Gateway chạy thêm vài ngày liên tục là đủ. SỬA MỘT HÌNH DẠNG LỖI, không chỉ thêm phép kiểm: mọi phép kiểm theo nguồn nay khai CẢ MẪU SỐ. Trước đây "0 dòng xấu" trên 0 dòng gateway báo ĐẠT — nó không phân biệt "Gateway ghi đúng" với "Gateway không ghi gì cả", và đó đúng là hình dạng đã để API mù 38 phút ngày 02/09. Nghiệm thu bằng cách tái tạo trên một tập rỗng THẬT (fact_perf_daily không có dòng gateway nào), không dựng database giả. NGHIỆM THU: audit_db.py 72 phép / 65 đạt / 7 lưu ý / 0 hỏng (mốc 68/64/4/0 — lưu ý tăng 4→7 là ĐÚNG, ba cái mới đều là chỗ trước nay báo đạt mà chưa quan sát gì, và bốn lưu ý cũ giữ nguyên); check_api.py 31/31 (mốc 27/27); chạy hai lần liên tiếp số không đổi; usage_resolved khớp 4/4 khoá — change này không đụng một dòng dữ liệu nào.</t>
+          <t>Đang làm. 31/08 scripts/audit_db.py đã có phép kiểm cho nguồn gateway: lượt hỏng không lọt vào bảng tổng hợp, không dòng nào có duration_ms = 0, không có giá trị outcome lạ. Chạy 01/09: 39 phép kiểm, 35 đạt, 4 lưu ý (đều là thiếu dữ liệu đã biết), 0 hỏng. 03/09: audit_db.py thêm nhóm F (12 phép) — tổng giờ khớp tổng ngày theo từng nguồn, không có billing trong bảng giờ, mọi giờ cắt đúng đầu giờ, phân vị số thô không mang ô histogram và ngược lại phân vị nội suy phải giữ ô. Chạy đầy đủ: 54 phép / 50 đạt / 4 lưu ý / 0 hỏng. backend/check_api.py XONG: thêm 6 phép cho endpoint theo giờ, chạy 25/25 đạt. Trong lúc làm, phát hiện check_api.py mang một phép kiểm LỖI THỜI từ 31/08 — nó so tiền API với riêng fact_billing_daily trong khi migration 005 đã cố ý đổ tiền Gateway vào usage_resolved ($307,360850 + $0,021305 = $307,382155), nên nó báo HỎNG cho một hệ thống đang đúng; đã sửa CÔNG THỨC theo đúng phép của audit_db.py, không nới ngưỡng. 03/09 chiều — XONG cả hai vế, nhưng vế 2 XONG theo nghĩa PHÉP KIỂM ĐÃ CÓ VÀ NÓ NÓI THẲNG LÀ CHƯA KIỂM ĐƯỢC, không phải theo nghĩa đã đối chiếu xong. VẾ 1 — bốn phép mà mục này liệt kê: KHOÁ NGOẠI nay đọc từ pg_constraint thay vì một danh sách gõ tay; đo được danh sách cũ đã trôi mất 13/36 quan hệ, trong đó 6 do chính migration 008 tạo ra sáng cùng ngày — nó tụt trong im lặng vì nhãn vẫn báo "Foreign keys (23 relations)" ĐẠT, mà 23 là số quan hệ ĐƯỢC KHAI chứ không phải số CÓ THẬT. Thêm mốc số lượng (&gt;= 36) để bắt chiều ngược lại: xoá một khoá ngoại thì danh sách tự sinh vẫn xanh. NGÀY TƯƠNG LAI bỏ ngưỡng ghim '2026-12-31' (sang 2027 mọi dòng thật đều bị coi là tương lai), thay bằng CURRENT_DATE + 1, và soi 5 bảng thay vì 1 — kể cả fact_call, nơi Gateway ghi từng lượt. TÀI KHOẢN LẠ và SỐ KHỚP HOÁ ĐƠN đã có từ 31/08, nay bổ sung mẫu số quan sát. VẾ 2 — phép kiểm đối chiếu token cache ĐÃ VIẾT XONG (nhóm H của audit_db.py), so theo ngày × agent trên đúng những ngày CẢ HAI nguồn cùng có, ngưỡng 1% chốt TRƯỚC kỳ đo theo đúng kỷ luật STT 7 dòng 19. Chạy hôm nay ra CHƯA KIỂM ĐƯỢC: gateway 31/08→31/08 (1 ngày), hoá đơn 05/01→29/08 (214 ngày), SỐ NGÀY GIAO NHAU = 0; và vế Gateway rỗng sạch (cached_tokens 0/41). ĐIỀU KIỆN ĐỂ NÓ CHẠY: một ngày mà Gateway và hoá đơn Google cùng có dữ liệu — hoá đơn về trễ ~1 ngày nên chỉ cần Gateway chạy thêm vài ngày liên tục là đủ. SỬA MỘT HÌNH DẠNG LỖI, không chỉ thêm phép kiểm: mọi phép kiểm theo nguồn nay khai CẢ MẪU SỐ. Trước đây "0 dòng xấu" trên 0 dòng gateway báo ĐẠT — nó không phân biệt "Gateway ghi đúng" với "Gateway không ghi gì cả", và đó đúng là hình dạng đã để API mù 38 phút ngày 02/09. Nghiệm thu bằng cách tái tạo trên một tập rỗng THẬT (fact_perf_daily không có dòng gateway nào), không dựng database giả. NGHIỆM THU: audit_db.py 72 phép / 65 đạt / 7 lưu ý / 0 hỏng (mốc 68/64/4/0 — lưu ý tăng 4→7 là ĐÚNG, ba cái mới đều là chỗ trước nay báo đạt mà chưa quan sát gì, và bốn lưu ý cũ giữ nguyên); check_api.py 31/31 (mốc 27/27); chạy hai lần liên tiếp số không đổi; usage_resolved khớp 4/4 khoá — change này không đụng một dòng dữ liệu nào. ĐÍNH CHÍNH 04/09: con số nghiệm thu ghi ở trên là 72/65/7/0, đo TRƯỚC commit 131d3b5 của cùng ngày 03/09. Sau commit đó bộ kiểm có thêm một phép (các bảng dẫn xuất từ Gateway phải mới ngang fact_call), nên mốc đúng là 73 phép / 66 đạt / 7 lưu ý / 0 hỏng. check_api.py giữ nguyên 31/31. 05/09 THÊM HAI NHÓM PHÉP KIỂM. NHÓM I — đối chiếu fact_call với số của CHÍNH NHÀ CUNG CẤP (bảng mới fact_provider_daily, migration 011), trên CẢ BA TRỤC và ở MỨC NGÀY. Ba trục chứ không một, vì ngày 31/08 số lượt khớp tuyệt đối 41/41 trong khi token lệch 6.334 — kiểm mỗi trục số lượt là phép kiểm xanh và lỗi đi qua. Mức ngày chứ không mức giờ, vì nhà cung cấp gắn nhãn ô theo thời điểm KẾT THÚC còn sổ ta ghi theo thời điểm BẮT ĐẦU: đo được giờ 01 lệch +1 lượt và giờ 02 lệch −1, cộng lại bằng 0 — một request rơi hai ô, không phải hai lỗi. HAI CHIỀU LỆCH XỬ LÝ KHÁC NHAU: nhà cung cấp nhiều hơn ta là chiều KỲ VỌNG nên LƯU Ý kèm số tuyệt đối và tỷ lệ, MUST NOT báo hỏng (báo hỏng thì phép kiểm đỏ vĩnh viễn rồi bị bỏ qua); ta nhiều hơn nhà cung cấp là HỎNG, không ngưỡng, vì ta không thể tiêu thứ họ không phục vụ. CHƯA ĐẶT NGƯỠNG PHẦN TRĂM cho chiều thiếu hụt, và đó là CHỦ Ý: đã biết đáp án 12,21% rồi mới viết phép kiểm, nên đặt ngưỡng bây giờ là chọn số vừa khít với đáp án — trái kỷ luật "ban hành ngưỡng trước kỳ đo" đã chốt ở dòng 19. NGHIỆM THU CHIỀU HỎNG BẰNG CÁCH TÁI TẠO LỖI, không chỉ đọc code: hạ vế nhà cung cấp xuống dưới fact_call thì audit đỏ đúng cả ba trục và thoát mã 1; nạp lại từ đợt kéo thì về nguyên trạng từng byte và xanh lại. NHÓM J — kế toán từng dòng sổ nguồn, TỰ TÍNH LẠI bằng SQL của riêng nó thay vì tin lời bộ nạp. HỎNG khi một dòng lẽ ra nạp được mà vắng mặt, và cả chiều ngược lại: dòng có trong fact_call mà sổ nguồn không còn. Đo được 47 dòng nguồn = 41 nạp + 5 không có tag định danh (408 token) + 1 bản sao cú cache hit (352 token), 0 dòng không giải thích được. Bản sao cache hit là phát hiện ngoài kế hoạch: LiteLLM ghi thêm một dòng mang request_id gốc cộng hậu tố _cache_hit&lt;epoch&gt; và LẶP LẠI nguyên token; hôm nay nó rớt vì một lý do chẳng liên quan, nên load_gateway.py nay loại nó tường minh — nếu không, ngày nào khâu định danh được nới ra là đếm đôi 352 token mà không phép kiểm nào bắt được. HỆ QUẢ CHO VẾ 2 CỦA MỤC NÀY: phép kiểm cache nhóm H sẽ KHÔNG BAO GIỜ chạy được cho lưu lượng Gateway, vì khoá là free tier nên không lên hoá đơn — nó vẫn đúng cho lưu lượng agent trả tiền. NGHIỆM THU: audit_db.py 78 phép / 68 đạt / 10 lưu ý / 0 hỏng (mốc 73/66/7/0 — tăng đúng 5 phép: nhóm I 2, nhóm J 3); chạy hai lần liên tiếp số không đổi; usage_resolved khớp 4/4 khoá mốc.</t>
         </is>
       </c>
       <c r="K20" s="17" t="n"/>

--- a/Master Plan API Gateway.xlsx
+++ b/Master Plan API Gateway.xlsx
@@ -80,7 +80,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +148,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -368,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -496,6 +502,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1539,8 +1549,8 @@
       <c r="K12" s="17" t="n"/>
       <c r="L12" s="17" t="n"/>
       <c r="M12" s="17" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="17" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
       <c r="P12" s="17" t="n"/>
       <c r="Q12" s="17" t="n"/>
       <c r="R12" s="17" t="n"/>
@@ -1846,8 +1856,8 @@
       <c r="K17" s="17" t="n"/>
       <c r="L17" s="17" t="n"/>
       <c r="M17" s="17" t="n"/>
-      <c r="N17" s="17" t="n"/>
-      <c r="O17" s="17" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
       <c r="P17" s="17" t="n"/>
       <c r="Q17" s="17" t="n"/>
       <c r="R17" s="17" t="n"/>
@@ -2140,12 +2150,16 @@
 (dự kiến)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="n"/>
+      <c r="J22" s="57" t="inlineStr">
+        <is>
+          <t>Đang làm. 31/08/2026 chuyển agent ĐẦU TIÊN (dms-feedback, chọn vì ít lưu lượng nhất theo đúng tiêu chí dòng này) qua Gateway thật: Virtual Key riêng mang tag "dms-feedback", đo bằng ba dấu vết độc lập trên 10 lượt gọi — 7/8 thành công, 1/8 trượt đúng vào tuyến mồi (kỳ vọng, không phải lỗi). Số của agent này đã vào fact_usage_daily với source='gateway' và qua được audit_db.py. 1/8 agent — 7 agent còn lại (Trợ lý ảo Ralli, Trợ Lý Ảo Hợp Đồng, Phân Loại Dữ Liệu CRM, Chatbot Contact Center, Sale Agent, Multi modal AI Invoice, Tools Quizzer) vẫn gọi thẳng nhà cung cấp, chưa có Virtual Key thật — chờ điều kiện ① (8 khoá API của 8 project) theo docs/reference/ke-hoach-nen-thang-9-2026.md. (trên một agent) — phép đo và phép kiểm ở trên mới xác nhận đúng cho 1/8 agent; dòng này chỉ tính XONG (tô xanh) khi cả 8 agent cùng chạy qua Gateway, không phải khi suy rộng từ kết quả của một agent duy nhất.</t>
+        </is>
+      </c>
       <c r="K22" s="17" t="n"/>
       <c r="L22" s="17" t="n"/>
       <c r="M22" s="17" t="n"/>
-      <c r="N22" s="17" t="n"/>
-      <c r="O22" s="17" t="n"/>
+      <c r="N22" s="58" t="n"/>
+      <c r="O22" s="58" t="n"/>
       <c r="P22" s="17" t="n"/>
       <c r="Q22" s="17" t="n"/>
       <c r="R22" s="17" t="n"/>
